--- a/Data/Figure1/Rawdata/HFDMiceKeyPhotometry.xlsx
+++ b/Data/Figure1/Rawdata/HFDMiceKeyPhotometry.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure1\Rawdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AC3355-783B-404F-826C-2031C87E85DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6665E50D-053F-4329-AB9B-21FCD89582EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="21">
   <si>
     <t>Name</t>
   </si>
@@ -76,6 +76,18 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>1855M5</t>
+  </si>
+  <si>
+    <t>1855M4</t>
+  </si>
+  <si>
+    <t>1855M3</t>
+  </si>
+  <si>
+    <t>1855M1</t>
   </si>
 </sst>
 </file>
@@ -393,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -588,6 +600,74 @@
         <v>31.5</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15">
+        <v>24.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
